--- a/artfynd/A 12708-2023 artfynd.xlsx
+++ b/artfynd/A 12708-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12708-2023 artfynd.xlsx
+++ b/artfynd/A 12708-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107503493</v>
+        <v>107504972</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596568.4743655224</v>
+        <v>596906</v>
       </c>
       <c r="R2" t="n">
-        <v>6422788.984114923</v>
+        <v>6422506</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +754,9 @@
           <t>2023-03-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-03-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,12 +787,7 @@
         <v>107503572</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596640.4324161607</v>
+        <v>596640</v>
       </c>
       <c r="R3" t="n">
-        <v>6422762.039625606</v>
+        <v>6422762</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,19 +863,9 @@
           <t>2023-03-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-03-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,51 +893,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107503739</v>
+        <v>107503622</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -976,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596717.557016107</v>
+        <v>596645</v>
       </c>
       <c r="R4" t="n">
-        <v>6422697.509640448</v>
+        <v>6422762</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,19 +972,9 @@
           <t>2023-03-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-03-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,12 +1005,7 @@
         <v>107503647</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596632.5061051582</v>
+        <v>596633</v>
       </c>
       <c r="R5" t="n">
-        <v>6422759.723674123</v>
+        <v>6422760</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,19 +1081,9 @@
           <t>2023-03-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-03-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,37 +1111,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107503622</v>
+        <v>107504935</v>
       </c>
       <c r="B6" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>102623</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1211,12 +1144,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1224,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596644.6999437326</v>
+        <v>596698</v>
       </c>
       <c r="R6" t="n">
-        <v>6422761.611537277</v>
+        <v>6422668</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1257,28 +1191,17 @@
           <t>2023-03-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-03-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1297,51 +1220,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107503533</v>
+        <v>107503789</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1349,13 +1271,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596578.3230301447</v>
+        <v>596698</v>
       </c>
       <c r="R7" t="n">
-        <v>6422799.84447437</v>
+        <v>6422668</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1382,28 +1304,17 @@
           <t>2023-03-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-03-21</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1422,55 +1333,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107503789</v>
+        <v>107503493</v>
       </c>
       <c r="B8" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1478,13 +1380,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596697.507551305</v>
+        <v>596568</v>
       </c>
       <c r="R8" t="n">
-        <v>6422668.343029048</v>
+        <v>6422789</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1511,27 +1413,18 @@
           <t>2023-03-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-03-21</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1547,6 +1440,226 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>107503533</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 12708, Snörum, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>596578</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6422800</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-03-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-03-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>107503739</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 12708, Snörum, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596718</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6422698</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-03-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-03-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
